--- a/Assets/Resources/CSV/CraftingRecipes.xlsx
+++ b/Assets/Resources/CSV/CraftingRecipes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UNITY GAME\类银河恶魔城\Assets\Resources\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4440F644-98E4-40B5-B14C-84D639D6302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7D8E35-0E61-4BC7-BE63-576282AA48C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配方" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="171">
   <si>
     <t>recipeId</t>
   </si>
@@ -175,9 +175,6 @@
     <t>110501</t>
   </si>
   <si>
-    <t>3000</t>
-  </si>
-  <si>
     <t>recipe_110502</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
     <t>110504</t>
   </si>
   <si>
-    <t>3500</t>
-  </si>
-  <si>
     <t>recipe_110505</t>
   </si>
   <si>
@@ -229,9 +223,6 @@
     <t>130004</t>
   </si>
   <si>
-    <t>5000</t>
-  </si>
-  <si>
     <t>recipe_110103</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>110203</t>
   </si>
   <si>
-    <t>6000</t>
-  </si>
-  <si>
     <t>recipe_110303</t>
   </si>
   <si>
@@ -307,9 +295,6 @@
     <t>100104</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>recipe_110104</t>
   </si>
   <si>
@@ -331,9 +316,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>12000</t>
-  </si>
-  <si>
     <t>recipe_110304</t>
   </si>
   <si>
@@ -391,9 +373,6 @@
     <t>130006</t>
   </si>
   <si>
-    <t>20000</t>
-  </si>
-  <si>
     <t>recipe_110105</t>
   </si>
   <si>
@@ -415,9 +394,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>24000</t>
-  </si>
-  <si>
     <t>recipe_110305</t>
   </si>
   <si>
@@ -475,9 +451,6 @@
     <t>130007</t>
   </si>
   <si>
-    <t>40000</t>
-  </si>
-  <si>
     <t>recipe_110106</t>
   </si>
   <si>
@@ -499,9 +472,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>48000</t>
-  </si>
-  <si>
     <t>recipe_110306</t>
   </si>
   <si>
@@ -554,9 +524,6 @@
   </si>
   <si>
     <t>100107</t>
-  </si>
-  <si>
-    <t>60000</t>
   </si>
   <si>
     <t>recipe_110207</t>
@@ -1262,8 +1229,8 @@
       <c r="G12" t="s">
         <v>14</v>
       </c>
-      <c r="H12" t="s">
-        <v>51</v>
+      <c r="H12">
+        <v>300</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -1271,13 +1238,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1291,8 +1258,8 @@
       <c r="G13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" t="s">
-        <v>51</v>
+      <c r="H13">
+        <v>300</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1300,13 +1267,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -1320,8 +1287,8 @@
       <c r="G14" t="s">
         <v>14</v>
       </c>
-      <c r="H14" t="s">
-        <v>51</v>
+      <c r="H14">
+        <v>300</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
@@ -1329,13 +1296,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -1349,8 +1316,8 @@
       <c r="G15" t="s">
         <v>20</v>
       </c>
-      <c r="H15" t="s">
-        <v>61</v>
+      <c r="H15">
+        <v>350</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1358,13 +1325,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1378,8 +1345,8 @@
       <c r="G16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" t="s">
-        <v>51</v>
+      <c r="H16">
+        <v>300</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
@@ -1387,16 +1354,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -1407,8 +1374,8 @@
       <c r="G17" t="s">
         <v>14</v>
       </c>
-      <c r="H17" t="s">
-        <v>69</v>
+      <c r="H17">
+        <v>500</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -1416,16 +1383,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -1436,8 +1403,8 @@
       <c r="G18" t="s">
         <v>14</v>
       </c>
-      <c r="H18" t="s">
-        <v>69</v>
+      <c r="H18">
+        <v>500</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
@@ -1445,16 +1412,16 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
@@ -1465,8 +1432,8 @@
       <c r="G19" t="s">
         <v>14</v>
       </c>
-      <c r="H19" t="s">
-        <v>76</v>
+      <c r="H19">
+        <v>600</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
@@ -1474,16 +1441,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -1494,8 +1461,8 @@
       <c r="G20" t="s">
         <v>14</v>
       </c>
-      <c r="H20" t="s">
-        <v>69</v>
+      <c r="H20">
+        <v>500</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
@@ -1503,16 +1470,16 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -1523,8 +1490,8 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
-      <c r="H21" t="s">
-        <v>69</v>
+      <c r="H21">
+        <v>500</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
@@ -1532,16 +1499,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -1552,8 +1519,8 @@
       <c r="G22" t="s">
         <v>14</v>
       </c>
-      <c r="H22" t="s">
-        <v>69</v>
+      <c r="H22">
+        <v>500</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
@@ -1561,16 +1528,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -1581,8 +1548,8 @@
       <c r="G23" t="s">
         <v>14</v>
       </c>
-      <c r="H23" t="s">
-        <v>69</v>
+      <c r="H23">
+        <v>500</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
@@ -1590,16 +1557,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -1610,8 +1577,8 @@
       <c r="G24" t="s">
         <v>14</v>
       </c>
-      <c r="H24" t="s">
-        <v>69</v>
+      <c r="H24">
+        <v>500</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
@@ -1619,13 +1586,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
         <v>19</v>
@@ -1639,8 +1606,8 @@
       <c r="G25" t="s">
         <v>14</v>
       </c>
-      <c r="H25" t="s">
-        <v>95</v>
+      <c r="H25">
+        <v>1000</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
@@ -1648,13 +1615,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>19</v>
@@ -1668,8 +1635,8 @@
       <c r="G26" t="s">
         <v>14</v>
       </c>
-      <c r="H26" t="s">
-        <v>95</v>
+      <c r="H26">
+        <v>1000</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
@@ -1677,19 +1644,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
@@ -1697,8 +1664,8 @@
       <c r="G27" t="s">
         <v>14</v>
       </c>
-      <c r="H27" t="s">
-        <v>103</v>
+      <c r="H27">
+        <v>1200</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
@@ -1706,13 +1673,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -1726,8 +1693,8 @@
       <c r="G28" t="s">
         <v>14</v>
       </c>
-      <c r="H28" t="s">
-        <v>95</v>
+      <c r="H28">
+        <v>1000</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
@@ -1735,13 +1702,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>19</v>
@@ -1755,8 +1722,8 @@
       <c r="G29" t="s">
         <v>14</v>
       </c>
-      <c r="H29" t="s">
-        <v>95</v>
+      <c r="H29">
+        <v>1000</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
@@ -1764,13 +1731,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>19</v>
@@ -1784,8 +1751,8 @@
       <c r="G30" t="s">
         <v>14</v>
       </c>
-      <c r="H30" t="s">
-        <v>95</v>
+      <c r="H30">
+        <v>1000</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
@@ -1793,13 +1760,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -1813,8 +1780,8 @@
       <c r="G31" t="s">
         <v>14</v>
       </c>
-      <c r="H31" t="s">
-        <v>95</v>
+      <c r="H31">
+        <v>1000</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
@@ -1822,13 +1789,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
@@ -1842,8 +1809,8 @@
       <c r="G32" t="s">
         <v>14</v>
       </c>
-      <c r="H32" t="s">
-        <v>95</v>
+      <c r="H32">
+        <v>1000</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
@@ -1851,19 +1818,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -1871,8 +1838,8 @@
       <c r="G33" t="s">
         <v>14</v>
       </c>
-      <c r="H33" t="s">
-        <v>123</v>
+      <c r="H33">
+        <v>2000</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
@@ -1880,16 +1847,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>32</v>
@@ -1900,8 +1867,8 @@
       <c r="G34" t="s">
         <v>14</v>
       </c>
-      <c r="H34" t="s">
-        <v>123</v>
+      <c r="H34">
+        <v>2000</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
@@ -1909,19 +1876,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -1929,8 +1896,8 @@
       <c r="G35" t="s">
         <v>14</v>
       </c>
-      <c r="H35" t="s">
-        <v>131</v>
+      <c r="H35">
+        <v>2400</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
@@ -1938,16 +1905,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s">
         <v>32</v>
@@ -1958,8 +1925,8 @@
       <c r="G36" t="s">
         <v>14</v>
       </c>
-      <c r="H36" t="s">
-        <v>123</v>
+      <c r="H36">
+        <v>2000</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
@@ -1967,16 +1934,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -1987,8 +1954,8 @@
       <c r="G37" t="s">
         <v>14</v>
       </c>
-      <c r="H37" t="s">
-        <v>123</v>
+      <c r="H37">
+        <v>2000</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
@@ -1996,16 +1963,16 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -2016,8 +1983,8 @@
       <c r="G38" t="s">
         <v>14</v>
       </c>
-      <c r="H38" t="s">
-        <v>123</v>
+      <c r="H38">
+        <v>2000</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
@@ -2025,16 +1992,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
         <v>32</v>
@@ -2045,8 +2012,8 @@
       <c r="G39" t="s">
         <v>14</v>
       </c>
-      <c r="H39" t="s">
-        <v>123</v>
+      <c r="H39">
+        <v>2000</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
@@ -2054,16 +2021,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -2074,8 +2041,8 @@
       <c r="G40" t="s">
         <v>14</v>
       </c>
-      <c r="H40" t="s">
-        <v>123</v>
+      <c r="H40">
+        <v>2000</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
@@ -2083,19 +2050,19 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -2103,8 +2070,8 @@
       <c r="G41" t="s">
         <v>14</v>
       </c>
-      <c r="H41" t="s">
-        <v>151</v>
+      <c r="H41">
+        <v>4000</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
@@ -2112,19 +2079,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -2132,8 +2099,8 @@
       <c r="G42" t="s">
         <v>14</v>
       </c>
-      <c r="H42" t="s">
-        <v>151</v>
+      <c r="H42">
+        <v>4000</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
@@ -2141,19 +2108,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E43" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -2161,8 +2128,8 @@
       <c r="G43" t="s">
         <v>14</v>
       </c>
-      <c r="H43" t="s">
-        <v>159</v>
+      <c r="H43">
+        <v>4800</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
@@ -2170,19 +2137,19 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -2190,8 +2157,8 @@
       <c r="G44" t="s">
         <v>14</v>
       </c>
-      <c r="H44" t="s">
-        <v>151</v>
+      <c r="H44">
+        <v>4000</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
@@ -2199,19 +2166,19 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -2219,8 +2186,8 @@
       <c r="G45" t="s">
         <v>14</v>
       </c>
-      <c r="H45" t="s">
-        <v>151</v>
+      <c r="H45">
+        <v>4000</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
@@ -2228,19 +2195,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -2248,8 +2215,8 @@
       <c r="G46" t="s">
         <v>14</v>
       </c>
-      <c r="H46" t="s">
-        <v>151</v>
+      <c r="H46">
+        <v>4000</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
@@ -2257,19 +2224,19 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
@@ -2277,8 +2244,8 @@
       <c r="G47" t="s">
         <v>14</v>
       </c>
-      <c r="H47" t="s">
-        <v>151</v>
+      <c r="H47">
+        <v>4000</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
@@ -2286,19 +2253,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -2306,8 +2273,8 @@
       <c r="G48" t="s">
         <v>14</v>
       </c>
-      <c r="H48" t="s">
-        <v>151</v>
+      <c r="H48">
+        <v>4000</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
@@ -2315,28 +2282,28 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
-      </c>
-      <c r="H49" t="s">
-        <v>178</v>
+        <v>97</v>
+      </c>
+      <c r="H49">
+        <v>6000</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
@@ -2344,28 +2311,28 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E50" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>32</v>
       </c>
-      <c r="H50" t="s">
-        <v>178</v>
+      <c r="H50">
+        <v>6000</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
